--- a/data/trans_bre/P16A06-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P16A06-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,52; 5,13</t>
+          <t>1,55; 5,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,72; 9,64</t>
+          <t>5,57; 9,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,47; 12,17</t>
+          <t>6,47; 12,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,09; 14,18</t>
+          <t>7,01; 14,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>31,99; 178,16</t>
+          <t>32,42; 184,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>147,72; 498,46</t>
+          <t>155,33; 570,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,71; 262,8</t>
+          <t>91,59; 262,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>51,55; 144,84</t>
+          <t>49,28; 140,99</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 2,17</t>
+          <t>0,33; 2,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,77</t>
+          <t>1,4; 3,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,06; 4,37</t>
+          <t>2,05; 4,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,16; 5,04</t>
+          <t>1,29; 5,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,91; 258,97</t>
+          <t>10,82; 245,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>56,66; 302,63</t>
+          <t>60,42; 282,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>97,85; 327,82</t>
+          <t>91,62; 345,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>29,82; 186,06</t>
+          <t>32,71; 183,97</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 2,54</t>
+          <t>-0,56; 2,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 3,04</t>
+          <t>-1,54; 3,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 3,39</t>
+          <t>-0,38; 3,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 3,71</t>
+          <t>-0,59; 3,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-45,03; 518,64</t>
+          <t>-43,91; 512,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-53,08; 411,16</t>
+          <t>-57,41; 388,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-28,64; 303,42</t>
+          <t>-23,29; 350,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 134,78</t>
+          <t>-11,66; 131,54</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,07</t>
+          <t>1,37; 3,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,27; 5,22</t>
+          <t>3,24; 5,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,91; 6,0</t>
+          <t>3,8; 5,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,09; 6,54</t>
+          <t>3,19; 6,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>58,98; 192,36</t>
+          <t>57,82; 186,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>133,85; 318,91</t>
+          <t>125,41; 313,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>126,09; 263,74</t>
+          <t>121,74; 267,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>65,04; 167,18</t>
+          <t>62,16; 156,18</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A06-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P16A06-Estudios-trans_bre.xlsx
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>97,58%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,55; 5,17</t>
+          <t>1,61; 5,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,57; 9,74</t>
+          <t>5,47; 9,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,47; 12,14</t>
+          <t>6,02; 12,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,01; 14,15</t>
+          <t>7,5; 13,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>32,42; 184,03</t>
+          <t>30,0; 176,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>155,33; 570,84</t>
+          <t>147,2; 499,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,59; 262,02</t>
+          <t>81,52; 261,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>49,28; 140,99</t>
+          <t>56,15; 148,92</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,3</t>
+          <t>3,65</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>89,54%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,16</t>
+          <t>0,32; 2,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,4; 3,82</t>
+          <t>1,38; 3,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,05; 4,47</t>
+          <t>2,01; 4,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,29; 5,02</t>
+          <t>2,49; 5,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,82; 245,66</t>
+          <t>10,75; 266,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>60,42; 282,4</t>
+          <t>59,61; 283,8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>91,62; 345,07</t>
+          <t>89,5; 348,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>32,71; 183,97</t>
+          <t>51,64; 143,88</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,62</t>
+          <t>1,77</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>45,54%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 2,41</t>
+          <t>-0,5; 2,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 3,03</t>
+          <t>-1,48; 3,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 3,7</t>
+          <t>-0,52; 3,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 3,73</t>
+          <t>-0,37; 3,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-43,91; 512,95</t>
+          <t>-52,08; 483,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-57,41; 388,99</t>
+          <t>-55,66; 462,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-23,29; 350,08</t>
+          <t>-23,35; 372,22</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,66; 131,54</t>
+          <t>-9,08; 133,56</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,98</t>
+          <t>5,22</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>102,51%</t>
+          <t>100,97%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,02</t>
+          <t>1,39; 3,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,24; 5,26</t>
+          <t>3,24; 5,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,8; 5,95</t>
+          <t>3,86; 5,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,19; 6,46</t>
+          <t>4,17; 6,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>57,82; 186,96</t>
+          <t>59,81; 182,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>125,41; 313,76</t>
+          <t>134,53; 325,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>121,74; 267,46</t>
+          <t>127,17; 265,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>62,16; 156,18</t>
+          <t>74,16; 137,4</t>
         </is>
       </c>
     </row>
